--- a/src/pandorafits/formats/visda/level1-headers.xlsx
+++ b/src/pandorafits/formats/visda/level1-headers.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lindseywiser/Desktop/Pandora/pandora-fits-main/src/pandorafits/formats/visda/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chedges/Pandora/repos/pandora-fits/src/pandorafits/formats/visda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB8469A7-0F61-1D41-8E2D-120DF1DDEDA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24065D35-6878-C94D-A0FF-E97377F2B324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4120" yWindow="760" windowWidth="26120" windowHeight="17060" activeTab="2" xr2:uid="{B6A127EC-86E5-1348-8EA3-CDC4E3346098}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17120" xr2:uid="{B6A127EC-86E5-1348-8EA3-CDC4E3346098}"/>
   </bookViews>
   <sheets>
-    <sheet name="Primary" sheetId="4" r:id="rId1"/>
-    <sheet name="Science" sheetId="6" r:id="rId2"/>
-    <sheet name="ROITABLE" sheetId="7" r:id="rId3"/>
+    <sheet name="Primary" sheetId="1" r:id="rId1"/>
+    <sheet name="Ext1" sheetId="2" r:id="rId2"/>
+    <sheet name="Ext2" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="98">
   <si>
     <t>SIMPLE</t>
   </si>
@@ -88,12 +88,21 @@
     <t>TARG_DEC</t>
   </si>
   <si>
+    <t>RICEX</t>
+  </si>
+  <si>
+    <t>RICEY</t>
+  </si>
+  <si>
+    <t>CORSTIME</t>
+  </si>
+  <si>
+    <t>FINETIME</t>
+  </si>
+  <si>
     <t>Name</t>
   </si>
   <si>
-    <t>Value</t>
-  </si>
-  <si>
     <t>Comment</t>
   </si>
   <si>
@@ -127,6 +136,9 @@
     <t>TUNIT1</t>
   </si>
   <si>
+    <t>SCIENCE</t>
+  </si>
+  <si>
     <t>IMAGE</t>
   </si>
   <si>
@@ -163,6 +175,15 @@
     <t>target declination [deg]</t>
   </si>
   <si>
+    <t>bit noise parameter for Rice compression</t>
+  </si>
+  <si>
+    <t>seconds since the TAI Epoch (Jan 1, 2000 at noo</t>
+  </si>
+  <si>
+    <t>nanoseconds added to CORSTIME seconds</t>
+  </si>
+  <si>
     <t>NASA Pandora</t>
   </si>
   <si>
@@ -208,6 +229,18 @@
     <t>length of dimension 2</t>
   </si>
   <si>
+    <t>PCOUNT</t>
+  </si>
+  <si>
+    <t>number of group parameters</t>
+  </si>
+  <si>
+    <t>GCOUNT</t>
+  </si>
+  <si>
+    <t>number of groups</t>
+  </si>
+  <si>
     <t>TFIELDS</t>
   </si>
   <si>
@@ -223,134 +256,89 @@
     <t>TFORM2</t>
   </si>
   <si>
+    <t>TUNIT2</t>
+  </si>
+  <si>
     <t>TBCOL2</t>
   </si>
   <si>
+    <t>NROI</t>
+  </si>
+  <si>
+    <t>number of regions of interest</t>
+  </si>
+  <si>
+    <t>ROISTRTX</t>
+  </si>
+  <si>
+    <t>region of interest origin in column</t>
+  </si>
+  <si>
+    <t>ROISTRTY</t>
+  </si>
+  <si>
+    <t>region of interest origin in row</t>
+  </si>
+  <si>
+    <t>ROISIZEX</t>
+  </si>
+  <si>
+    <t>region of interest size in column</t>
+  </si>
+  <si>
+    <t>ROISIZEY</t>
+  </si>
+  <si>
+    <t>region of interest size in row</t>
+  </si>
+  <si>
     <t>TABLE</t>
   </si>
   <si>
-    <t>PCOUNT</t>
-  </si>
-  <si>
-    <t>number of group parameters</t>
-  </si>
-  <si>
-    <t>number of groups</t>
-  </si>
-  <si>
-    <t>GCOUNT</t>
-  </si>
-  <si>
-    <t>TUNIT2</t>
+    <t>COLUMN</t>
+  </si>
+  <si>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>units: pixels</t>
+  </si>
+  <si>
+    <t>pix</t>
+  </si>
+  <si>
+    <t>ROW</t>
+  </si>
+  <si>
+    <t>Row</t>
   </si>
   <si>
     <t>ROITABLE</t>
   </si>
   <si>
-    <t>NROI</t>
-  </si>
-  <si>
-    <t>ROISTRTX</t>
-  </si>
-  <si>
-    <t>ROISTRTY</t>
-  </si>
-  <si>
-    <t>ROISIZEX</t>
-  </si>
-  <si>
-    <t>ROISIZEY</t>
-  </si>
-  <si>
-    <t>pix</t>
-  </si>
-  <si>
-    <t>Column</t>
-  </si>
-  <si>
-    <t>I21</t>
-  </si>
-  <si>
-    <t>Row</t>
-  </si>
-  <si>
-    <t>region of interest size in row</t>
-  </si>
-  <si>
-    <t>region of interest size in column</t>
-  </si>
-  <si>
-    <t>region of interest origin position in row</t>
-  </si>
-  <si>
-    <t>region of interest origin position in column</t>
-  </si>
-  <si>
-    <t>number of regions of interest</t>
-  </si>
-  <si>
-    <t>name of extention</t>
-  </si>
-  <si>
-    <t>SCIENCE</t>
-  </si>
-  <si>
-    <t>COUNTS</t>
-  </si>
-  <si>
-    <t>data title: raw pixel counts</t>
-  </si>
-  <si>
-    <t>data format: images of unsigned 32-bit integers</t>
-  </si>
-  <si>
-    <t>data units: count</t>
-  </si>
-  <si>
-    <t>J</t>
-  </si>
-  <si>
-    <t>count</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>Pandora MOC</t>
+    <t>Fixed Value</t>
+  </si>
+  <si>
+    <t>Example Value</t>
   </si>
   <si>
     <t>v0.1.0</t>
   </si>
   <si>
-    <t xml:space="preserve">bit noise parameter for Rice compression </t>
-  </si>
-  <si>
-    <t>seconds since the TAI Epoch (Jan1, 2000 at noon)</t>
-  </si>
-  <si>
-    <t>nanoseconds added to CORSTIME seconds</t>
-  </si>
-  <si>
-    <t>RICEX</t>
-  </si>
-  <si>
-    <t>RICEY</t>
-  </si>
-  <si>
-    <t>CORSTIME</t>
-  </si>
-  <si>
-    <t>FINETIME</t>
+    <t>Pandora DPC</t>
+  </si>
+  <si>
+    <t>format</t>
+  </si>
+  <si>
+    <t>F13.9</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -371,18 +359,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Menlo"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -405,13 +381,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -745,273 +719,302 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D1C3A0A-8A3B-0648-AAEB-8D3739DF90A8}">
-  <dimension ref="A1:C24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81127257-918B-0849-8077-19480435CD41}">
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="41.5" customWidth="1"/>
-    <col min="3" max="3" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2" t="b">
+        <v>1</v>
+      </c>
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B5" t="b">
+        <v>1</v>
+      </c>
+      <c r="C5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
       <c r="B7">
         <v>3</v>
       </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C9" t="b">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+      <c r="D10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+      <c r="D11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B12" t="s">
-        <v>93</v>
-      </c>
       <c r="C12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+      <c r="D12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>94</v>
       </c>
-      <c r="C13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="5">
+      <c r="C14">
         <v>153.71574452308701</v>
       </c>
-      <c r="C14" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="5">
+      <c r="C15">
         <v>-47.156720216140499</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16">
         <v>40</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16">
+      <c r="D16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17">
         <v>40</v>
       </c>
-      <c r="C16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17">
-        <v>40</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19">
+        <v>0.2</v>
+      </c>
+      <c r="D19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20">
+        <v>32</v>
+      </c>
+      <c r="D20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21">
+        <v>5</v>
+      </c>
+      <c r="D21" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22">
+        <v>10</v>
+      </c>
+      <c r="D22" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23">
+        <v>744941360</v>
+      </c>
+      <c r="D23" t="s">
         <v>46</v>
       </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18" t="s">
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24">
+        <v>792000000</v>
+      </c>
+      <c r="D24" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>48</v>
-      </c>
-      <c r="B19">
-        <v>0.2</v>
-      </c>
-      <c r="C19" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>50</v>
-      </c>
-      <c r="B20">
-        <v>32</v>
-      </c>
-      <c r="C20" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>98</v>
-      </c>
-      <c r="B21">
-        <v>5</v>
-      </c>
-      <c r="C21" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>99</v>
-      </c>
-      <c r="B22">
-        <v>10</v>
-      </c>
-      <c r="C22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>100</v>
-      </c>
-      <c r="B23" s="5">
-        <v>744941360</v>
-      </c>
-      <c r="C23" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>101</v>
-      </c>
-      <c r="B24">
-        <v>792000000</v>
-      </c>
-      <c r="C24" t="s">
-        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1020,123 +1023,136 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFF9BC8E-79D6-3D4F-A83E-F2C79C6EF671}">
-  <dimension ref="A1:C11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83271CB-FC54-E142-86E3-37282DC63805}">
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>93</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>32</v>
-      </c>
-      <c r="C3" t="s">
+        <v>-32</v>
+      </c>
+      <c r="C3">
+        <v>-32</v>
+      </c>
+      <c r="D3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5">
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6">
         <v>150</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" t="s">
-        <v>89</v>
-      </c>
-      <c r="C10" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
         <v>28</v>
       </c>
-      <c r="B11" t="s">
-        <v>90</v>
-      </c>
-      <c r="C11" t="s">
-        <v>88</v>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1145,252 +1161,312 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8EBF481-E44A-834F-A33B-E0886CC2A2D3}">
-  <dimension ref="A1:C28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D1C3A0A-8A3B-0648-AAEB-8D3739DF90A8}">
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+      <c r="D2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B5">
-        <v>42</v>
-      </c>
-      <c r="C5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+      <c r="C5">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+      <c r="C6">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>63</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9" s="3">
+        <v>67</v>
+      </c>
+      <c r="B9">
         <v>2</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C9" s="2">
+        <v>2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+      <c r="C10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+      <c r="C11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="C12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>58</v>
-      </c>
-      <c r="B13" s="4">
+        <v>69</v>
+      </c>
+      <c r="B13">
         <v>1</v>
       </c>
-      <c r="C13" s="4"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+      <c r="C14" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+      <c r="C15" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>67</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+        <v>72</v>
+      </c>
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="B17">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+      <c r="C17">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="2">
+        <v>9</v>
+      </c>
+      <c r="D19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20">
+        <v>512</v>
+      </c>
+      <c r="D20" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21">
+        <v>512</v>
+      </c>
+      <c r="D21" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>80</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1024</v>
+      </c>
+      <c r="D22" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23">
+        <v>1024</v>
+      </c>
+      <c r="D23" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>69</v>
-      </c>
-      <c r="B19" s="3">
-        <v>9</v>
-      </c>
-      <c r="C19" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20">
-        <v>512</v>
-      </c>
-      <c r="C20" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21">
-        <v>512</v>
-      </c>
-      <c r="C21" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>72</v>
-      </c>
-      <c r="B22" s="3">
-        <v>1024</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>73</v>
-      </c>
-      <c r="B23">
-        <v>1024</v>
-      </c>
-      <c r="C23" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
